--- a/www/flightdata/xlsx/eoss-307.xlsx
+++ b/www/flightdata/xlsx/eoss-307.xlsx
@@ -5154,7 +5154,7 @@
         <v>31915</v>
       </c>
       <c r="I2">
-        <v>979</v>
+        <v>721</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
